--- a/2VAR_ATSBR_T2W/2var_atsbr_t2w_CARPOOL.xlsx
+++ b/2VAR_ATSBR_T2W/2var_atsbr_t2w_CARPOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/philliao/Downloads/Code/IB-Math-IA/2VAR_ATSBR_T2W/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{167DFCAE-1D25-0343-84A5-3ED429DD7487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{59A152CC-5930-474C-9291-C5DADA0E5436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="25600" windowHeight="16000" xr2:uid="{90DD965B-7C23-E944-BE8B-C22836C14490}"/>
+    <workbookView xWindow="3840" yWindow="660" windowWidth="21760" windowHeight="14320" xr2:uid="{90DD965B-7C23-E944-BE8B-C22836C14490}"/>
   </bookViews>
   <sheets>
     <sheet name="2var_atsbr_t2w_CARPOOL.xlsx" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="16" uniqueCount="5">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="118" uniqueCount="31">
   <si>
     <t>district_name</t>
   </si>
@@ -53,12 +53,90 @@
   <si>
     <t>r value</t>
   </si>
+  <si>
+    <t>SUMMARY OUTPUT</t>
+  </si>
+  <si>
+    <t>Regression Statistics</t>
+  </si>
+  <si>
+    <t>Multiple R</t>
+  </si>
+  <si>
+    <t>R Square</t>
+  </si>
+  <si>
+    <t>Adjusted R Square</t>
+  </si>
+  <si>
+    <t>Standard Error</t>
+  </si>
+  <si>
+    <t>Observations</t>
+  </si>
+  <si>
+    <t>ANOVA</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Significance F</t>
+  </si>
+  <si>
+    <t>Coefficients</t>
+  </si>
+  <si>
+    <t>t Stat</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Lower 95%</t>
+  </si>
+  <si>
+    <t>Upper 95%</t>
+  </si>
+  <si>
+    <t>Lower 95.0%</t>
+  </si>
+  <si>
+    <t>Upper 95.0%</t>
+  </si>
+  <si>
+    <t>speed_acr_rank</t>
+  </si>
+  <si>
+    <t>rho=</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -196,6 +274,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -382,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <start/>
       <end/>
@@ -497,8 +583,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <start/>
+      <end/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <start/>
+      <end/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -541,12 +647,22 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -586,6 +702,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="42" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -638,7 +755,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion Rate to Carpool Rate</a:t>
+              <a:t>ATSBR CARPOOL</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -719,8 +836,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="4.3517936381187269E-2"/>
-                  <c:y val="0.21300498511511565"/>
+                  <c:x val="-2.8369098278633015E-2"/>
+                  <c:y val="0.40539872113301284"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -1099,6 +1216,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1106,7 +1224,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1176,7 +1293,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion Rate to Carpool Rate</a:t>
+              <a:t>ATSBR CARPOOL (Crowded)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1293,7 +1410,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'2var_atsbr_t2w_CARPOOL.xlsx'!$C$18:$C$29</c:f>
+              <c:f>'2var_atsbr_t2w_CARPOOL.xlsx'!$Q$2:$Q$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1311,7 +1428,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'2var_atsbr_t2w_CARPOOL.xlsx'!$B$18:$B$29</c:f>
+              <c:f>'2var_atsbr_t2w_CARPOOL.xlsx'!$P$2:$P$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1589,6 +1706,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1596,7 +1714,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1666,7 +1783,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Congestion Rate to Carpool Rate</a:t>
+              <a:t>ATSBR CARPOOL</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0%"/>
+              <a:t> (Uncrowded)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1747,8 +1868,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="4.3517936381187269E-2"/>
-                  <c:y val="0.21300498511511565"/>
+                  <c:x val="4.0832886903257759E-2"/>
+                  <c:y val="0.27817400341735804"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -1783,7 +1904,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'2var_atsbr_t2w_CARPOOL.xlsx'!$C$34:$C$45</c:f>
+              <c:f>'2var_atsbr_t2w_CARPOOL.xlsx'!$AE$2:$AE$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1816,7 +1937,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'2var_atsbr_t2w_CARPOOL.xlsx'!$B$34:$B$45</c:f>
+              <c:f>'2var_atsbr_t2w_CARPOOL.xlsx'!$AD$2:$AD$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2109,6 +2230,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2116,7 +2238,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3859,15 +3980,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>819150</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>196850</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3897,15 +4018,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>819150</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>196850</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4253,10 +4374,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D564F2-7991-2B47-9E93-FCDC568DD205}">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:AO50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4266,8 +4387,26 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4277,8 +4416,20 @@
       <c r="C2">
         <v>25.331689999999998</v>
       </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="AC2">
+        <v>1</v>
+      </c>
+      <c r="AD2">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="AE2">
+        <v>25.331689999999998</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4288,8 +4439,20 @@
       <c r="C3">
         <v>10.98541</v>
       </c>
+      <c r="O3">
+        <v>2</v>
+      </c>
+      <c r="AC3">
+        <v>2</v>
+      </c>
+      <c r="AD3">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="AE3">
+        <v>10.98541</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4306,8 +4469,34 @@
         <f>CORREL(C2:C13, B2:B13)</f>
         <v>0.57969270187699318</v>
       </c>
+      <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z4">
+        <f>CORREL(Q2:Q13, P2:P13)</f>
+        <v>0.99023241660327244</v>
+      </c>
+      <c r="AC4">
+        <v>3</v>
+      </c>
+      <c r="AD4">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="AE4">
+        <v>39.341079999999998</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN4">
+        <f>CORREL(AE2:AE13, AD2:AD13)</f>
+        <v>0.42538947809582711</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4317,8 +4506,20 @@
       <c r="C5">
         <v>12.56434</v>
       </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5">
+        <v>3.0647164000000001E-2</v>
+      </c>
+      <c r="Q5">
+        <v>12.56434</v>
+      </c>
+      <c r="AC5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4328,8 +4529,20 @@
       <c r="C6">
         <v>24.90231</v>
       </c>
+      <c r="O6">
+        <v>5</v>
+      </c>
+      <c r="AC6">
+        <v>5</v>
+      </c>
+      <c r="AD6">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="AE6">
+        <v>24.90231</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4339,8 +4552,20 @@
       <c r="C7">
         <v>23.705850000000002</v>
       </c>
+      <c r="O7">
+        <v>6</v>
+      </c>
+      <c r="AC7">
+        <v>6</v>
+      </c>
+      <c r="AD7">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="AE7">
+        <v>23.705850000000002</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4350,8 +4575,20 @@
       <c r="C8">
         <v>44.66028</v>
       </c>
+      <c r="O8">
+        <v>7</v>
+      </c>
+      <c r="P8">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="Q8">
+        <v>44.66028</v>
+      </c>
+      <c r="AC8">
+        <v>7</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4361,16 +4598,34 @@
       <c r="C9">
         <v>33.988129999999998</v>
       </c>
+      <c r="O9">
+        <v>8</v>
+      </c>
+      <c r="AC9">
+        <v>8</v>
+      </c>
+      <c r="AD9">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="AE9">
+        <v>33.988129999999998</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="D10">
         <v>-0.220663843</v>
       </c>
+      <c r="O10">
+        <v>9</v>
+      </c>
+      <c r="AC10">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4380,8 +4635,20 @@
       <c r="C11">
         <v>20.73094</v>
       </c>
+      <c r="O11">
+        <v>10</v>
+      </c>
+      <c r="AC11">
+        <v>10</v>
+      </c>
+      <c r="AD11">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="AE11">
+        <v>20.73094</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4391,8 +4658,20 @@
       <c r="C12">
         <v>10.663930000000001</v>
       </c>
+      <c r="O12">
+        <v>11</v>
+      </c>
+      <c r="AC12">
+        <v>11</v>
+      </c>
+      <c r="AD12">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="AE12">
+        <v>10.663930000000001</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4402,93 +4681,426 @@
       <c r="C13">
         <v>49.626179999999998</v>
       </c>
+      <c r="O13">
+        <v>12</v>
+      </c>
+      <c r="P13">
+        <v>5.5304152000000002E-2</v>
+      </c>
+      <c r="Q13">
+        <v>49.626179999999998</v>
+      </c>
+      <c r="AC13">
+        <v>12</v>
+      </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>1</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>2</v>
       </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" t="s">
+        <v>0</v>
+      </c>
+      <c r="P18" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>2</v>
+      </c>
+      <c r="S18" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18">
+    <row r="19" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>1</v>
       </c>
+      <c r="B19">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="C19">
+        <v>25.331689999999998</v>
+      </c>
+      <c r="O19">
+        <v>4</v>
+      </c>
+      <c r="P19">
+        <v>3.0647164000000001E-2</v>
+      </c>
+      <c r="Q19">
+        <v>12.56434</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="AE19">
+        <v>25.331689999999998</v>
+      </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>2</v>
       </c>
+      <c r="B20">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="C20">
+        <v>10.98541</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="O20">
+        <v>7</v>
+      </c>
+      <c r="P20">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="Q20">
+        <v>44.66028</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T20" s="4"/>
+      <c r="AC20">
+        <v>2</v>
+      </c>
+      <c r="AD20">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="AE20">
+        <v>10.98541</v>
+      </c>
+      <c r="AG20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH20" s="4"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>3</v>
       </c>
-      <c r="K20" t="s">
+      <c r="B21">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="C21">
+        <v>39.341079999999998</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21">
+        <v>0.57969270187699307</v>
+      </c>
+      <c r="O21">
+        <v>12</v>
+      </c>
+      <c r="P21">
+        <v>5.5304152000000002E-2</v>
+      </c>
+      <c r="Q21">
+        <v>49.626179999999998</v>
+      </c>
+      <c r="S21" t="s">
+        <v>7</v>
+      </c>
+      <c r="T21">
+        <v>0.99023241660327244</v>
+      </c>
+      <c r="AC21">
+        <v>3</v>
+      </c>
+      <c r="AD21">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="AE21">
+        <v>39.341079999999998</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH21">
+        <v>0.42538947809582683</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>4</v>
       </c>
-      <c r="L20">
-        <f>CORREL(C18:C29, B18:B29)</f>
-        <v>0.99023241660327244</v>
+      <c r="B22">
+        <v>3.0647164000000001E-2</v>
+      </c>
+      <c r="C22">
+        <v>12.56434</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>0.33604362860944836</v>
+      </c>
+      <c r="S22" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22">
+        <v>0.98056023889195687</v>
+      </c>
+      <c r="AC22">
+        <v>5</v>
+      </c>
+      <c r="AD22">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="AE22">
+        <v>24.90231</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH22">
+        <v>0.18095620807463994</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>4</v>
-      </c>
-      <c r="B21">
-        <v>3.0647164000000001E-2</v>
-      </c>
-      <c r="C21">
-        <v>12.56434</v>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="C23">
+        <v>24.90231</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23">
+        <v>0.26227069845494261</v>
+      </c>
+      <c r="S23" t="s">
+        <v>9</v>
+      </c>
+      <c r="T23">
+        <v>0.96112047778391374</v>
+      </c>
+      <c r="AC23">
+        <v>6</v>
+      </c>
+      <c r="AD23">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="AE23">
+        <v>23.705850000000002</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH23">
+        <v>4.4448909420413261E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>5</v>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="C24">
+        <v>23.705850000000002</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>3.102037152226584E-2</v>
+      </c>
+      <c r="S24" t="s">
+        <v>10</v>
+      </c>
+      <c r="T24">
+        <v>2.8337696498684454E-3</v>
+      </c>
+      <c r="AC24">
+        <v>8</v>
+      </c>
+      <c r="AD24">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="AE24">
+        <v>33.988129999999998</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH24">
+        <v>3.1387240876481586E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>6</v>
+    <row r="25" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>7</v>
+      </c>
+      <c r="B25">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="C25">
+        <v>44.66028</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2">
+        <v>11</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T25" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC25">
+        <v>10</v>
+      </c>
+      <c r="AD25">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="AE25">
+        <v>20.73094</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH25" s="2">
+        <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>7</v>
-      </c>
-      <c r="B24">
-        <v>5.5768249999999998E-2</v>
-      </c>
-      <c r="C24">
-        <v>44.66028</v>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="C26">
+        <v>33.988129999999998</v>
+      </c>
+      <c r="AC26">
+        <v>11</v>
+      </c>
+      <c r="AD26">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="AE26">
+        <v>10.663930000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>10</v>
       </c>
+      <c r="B27">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="C27">
+        <v>20.73094</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="S27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>11</v>
       </c>
+      <c r="B28">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="C28">
+        <v>10.663930000000001</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL28" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>12</v>
       </c>
@@ -4498,135 +5110,839 @@
       <c r="C29">
         <v>49.626179999999998</v>
       </c>
+      <c r="E29" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>4.3832134704486683E-3</v>
+      </c>
+      <c r="H29">
+        <v>4.3832134704486683E-3</v>
+      </c>
+      <c r="I29">
+        <v>4.5551075158009606</v>
+      </c>
+      <c r="J29" s="5">
+        <v>6.1592477104694308E-2</v>
+      </c>
+      <c r="S29" t="s">
+        <v>13</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29">
+        <v>4.0505355157319906E-4</v>
+      </c>
+      <c r="V29">
+        <v>4.0505355157319906E-4</v>
+      </c>
+      <c r="W29">
+        <v>50.440961359666723</v>
+      </c>
+      <c r="X29" s="5">
+        <v>8.905182417235355E-2</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH29">
+        <v>1</v>
+      </c>
+      <c r="AI29">
+        <v>1.3059420178529527E-3</v>
+      </c>
+      <c r="AJ29">
+        <v>1.3059420178529527E-3</v>
+      </c>
+      <c r="AK29">
+        <v>1.3256156253813391</v>
+      </c>
+      <c r="AL29" s="5">
+        <v>0.29339227147952818</v>
+      </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30">
+        <v>9</v>
+      </c>
+      <c r="G30">
+        <v>8.6603710444146127E-3</v>
+      </c>
+      <c r="H30">
+        <v>9.6226344937940141E-4</v>
+      </c>
+      <c r="S30" t="s">
+        <v>14</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+      <c r="U30">
+        <v>8.0302504285155315E-6</v>
+      </c>
+      <c r="V30">
+        <v>8.0302504285155315E-6</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH30">
+        <v>6</v>
+      </c>
+      <c r="AI30">
+        <v>5.9109533390296586E-3</v>
+      </c>
+      <c r="AJ30">
+        <v>9.851588898382765E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1.3043584514863281E-2</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="S31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T31" s="2">
+        <v>2</v>
+      </c>
+      <c r="U31" s="2">
+        <v>4.1308380200171457E-4</v>
+      </c>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="AG31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH31" s="2">
+        <v>7</v>
+      </c>
+      <c r="AI31" s="2">
+        <v>7.2168953568826112E-3</v>
+      </c>
+      <c r="AJ31" s="2"/>
+      <c r="AK31" s="2"/>
+      <c r="AL31" s="2"/>
+    </row>
+    <row r="32" spans="1:38" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG33" s="3"/>
+      <c r="AH33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AK33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AM33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AN33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO33" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="E34" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34">
+        <v>-3.088663873962498E-2</v>
+      </c>
+      <c r="G34">
+        <v>2.1745953906774883E-2</v>
+      </c>
+      <c r="H34">
+        <v>-1.4203395662492573</v>
+      </c>
+      <c r="I34" s="5">
+        <v>0.18921085016973541</v>
+      </c>
+      <c r="J34">
+        <v>-8.0079404131715395E-2</v>
+      </c>
+      <c r="K34">
+        <v>1.8306126652465438E-2</v>
+      </c>
+      <c r="L34">
+        <v>-8.0079404131715395E-2</v>
+      </c>
+      <c r="M34">
+        <v>1.8306126652465438E-2</v>
+      </c>
+      <c r="S34" t="s">
+        <v>16</v>
+      </c>
+      <c r="T34">
+        <v>2.2044864842721702E-2</v>
+      </c>
+      <c r="U34">
+        <v>3.9065986708292011E-3</v>
+      </c>
+      <c r="V34">
+        <v>5.6429817087002014</v>
+      </c>
+      <c r="W34" s="5">
+        <v>0.1116570141727021</v>
+      </c>
+      <c r="X34">
+        <v>-2.7593177690902092E-2</v>
+      </c>
+      <c r="Y34">
+        <v>7.16829073763455E-2</v>
+      </c>
+      <c r="Z34">
+        <v>-2.7593177690902092E-2</v>
+      </c>
+      <c r="AA34">
+        <v>7.16829073763455E-2</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH34">
+        <v>-3.5067944117655472E-2</v>
+      </c>
+      <c r="AI34">
+        <v>3.0327187257400183E-2</v>
+      </c>
+      <c r="AJ34">
+        <v>-1.1563203610021069</v>
+      </c>
+      <c r="AK34" s="5">
+        <v>0.29150702864176903</v>
+      </c>
+      <c r="AL34">
+        <v>-0.10927589802968068</v>
+      </c>
+      <c r="AM34">
+        <v>3.9140009794369747E-2</v>
+      </c>
+      <c r="AN34">
+        <v>-0.10927589802968068</v>
+      </c>
+      <c r="AO34">
+        <v>3.9140009794369747E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:41" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1.5544525514756072E-3</v>
+      </c>
+      <c r="G35" s="2">
+        <v>7.2832992449776686E-4</v>
+      </c>
+      <c r="H35" s="2">
+        <v>2.1342697851492347</v>
+      </c>
+      <c r="I35" s="6">
+        <v>6.1592477104694385E-2</v>
+      </c>
+      <c r="J35" s="2">
+        <v>-9.3144204107292226E-5</v>
+      </c>
+      <c r="K35" s="2">
+        <v>3.2020493070585064E-3</v>
+      </c>
+      <c r="L35" s="2">
+        <v>-9.3144204107292226E-5</v>
+      </c>
+      <c r="M35" s="2">
+        <v>3.2020493070585064E-3</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="T35" s="2">
+        <v>7.0738797904961771E-4</v>
+      </c>
+      <c r="U35" s="2">
+        <v>9.9601527248174479E-5</v>
+      </c>
+      <c r="V35" s="2">
+        <v>7.1021800427521349</v>
+      </c>
+      <c r="W35" s="6">
+        <v>8.9051824172353564E-2</v>
+      </c>
+      <c r="X35" s="2">
+        <v>-5.5816941820137063E-4</v>
+      </c>
+      <c r="Y35" s="2">
+        <v>1.9729453763006059E-3</v>
+      </c>
+      <c r="Z35" s="2">
+        <v>-5.5816941820137063E-4</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>1.9729453763006059E-3</v>
+      </c>
+      <c r="AG35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH35" s="2">
+        <v>1.3707738710888413E-3</v>
+      </c>
+      <c r="AI35" s="2">
+        <v>1.1905756891490175E-3</v>
+      </c>
+      <c r="AJ35" s="2">
+        <v>1.1513538228456717</v>
+      </c>
+      <c r="AK35" s="6">
+        <v>0.29339227147952762</v>
+      </c>
+      <c r="AL35" s="2">
+        <v>-1.5424598923749792E-3</v>
+      </c>
+      <c r="AM35" s="2">
+        <v>4.2840076345526616E-3</v>
+      </c>
+      <c r="AN35" s="2">
+        <v>-1.5424598923749792E-3</v>
+      </c>
+      <c r="AO35" s="2">
+        <v>4.2840076345526616E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>0</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B39" t="s">
         <v>1</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" t="s">
         <v>2</v>
       </c>
+      <c r="O39" t="s">
+        <v>0</v>
+      </c>
+      <c r="P39" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>29</v>
+      </c>
+      <c r="R39" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>1</v>
       </c>
-      <c r="B34">
+      <c r="B40">
         <v>-8.9864090000000008E-3</v>
       </c>
-      <c r="C34">
+      <c r="C40">
+        <f>_xlfn.RANK.AVG(B40, B$40:B$50, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="D40">
         <v>25.331689999999998</v>
       </c>
+      <c r="E40">
+        <f>_xlfn.RANK.AVG(D40, D$40:D$50, 1)</f>
+        <v>7</v>
+      </c>
+      <c r="O40">
+        <v>4</v>
+      </c>
+      <c r="P40">
+        <v>3.0647164000000001E-2</v>
+      </c>
+      <c r="Q40">
+        <f>_xlfn.RANK.AVG(P40, P$40:P$42)</f>
+        <v>3</v>
+      </c>
+      <c r="R40">
+        <v>12.56434</v>
+      </c>
+      <c r="S40">
+        <f>_xlfn.RANK.AVG(R40, R$40:R$42)</f>
+        <v>3</v>
+      </c>
+      <c r="AC40">
+        <v>1</v>
+      </c>
+      <c r="AD40">
+        <v>-8.9864090000000008E-3</v>
+      </c>
+      <c r="AE40">
+        <f>_xlfn.RANK.AVG(AD40, AD$40:AD$47, 1)</f>
+        <v>3</v>
+      </c>
+      <c r="AF40">
+        <v>25.331689999999998</v>
+      </c>
+      <c r="AG40">
+        <f>_xlfn.RANK.AVG(AF40, AF$40:AF$47, 1)</f>
+        <v>6</v>
+      </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A41">
         <v>2</v>
       </c>
-      <c r="B35">
+      <c r="B41">
         <v>-7.0764041999999999E-2</v>
       </c>
-      <c r="C35">
+      <c r="C41">
+        <f t="shared" ref="C41:C50" si="0">_xlfn.RANK.AVG(B41, B$40:B$50, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="D41">
         <v>10.98541</v>
       </c>
+      <c r="E41">
+        <f t="shared" ref="E41:E50" si="1">_xlfn.RANK.AVG(D41, D$40:D$50, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="G41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H41">
+        <f>CORREL(C40:C50, E40:E50)</f>
+        <v>0.39090909090909087</v>
+      </c>
+      <c r="O41">
+        <v>7</v>
+      </c>
+      <c r="P41">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" ref="Q41:Q42" si="2">_xlfn.RANK.AVG(P41, P$40:P$42)</f>
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <v>44.66028</v>
+      </c>
+      <c r="S41">
+        <f t="shared" ref="S41:S42" si="3">_xlfn.RANK.AVG(R41, R$40:R$42)</f>
+        <v>2</v>
+      </c>
+      <c r="U41" t="s">
+        <v>30</v>
+      </c>
+      <c r="V41">
+        <f>CORREL(Q40:Q42, S40:S42)</f>
+        <v>0.5</v>
+      </c>
+      <c r="AC41">
+        <v>2</v>
+      </c>
+      <c r="AD41">
+        <v>-7.0764041999999999E-2</v>
+      </c>
+      <c r="AE41">
+        <f t="shared" ref="AE41:AE47" si="4">_xlfn.RANK.AVG(AD41, AD$40:AD$47, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="AF41">
+        <v>10.98541</v>
+      </c>
+      <c r="AG41">
+        <f t="shared" ref="AG41:AG47" si="5">_xlfn.RANK.AVG(AF41, AF$40:AF$47, 1)</f>
+        <v>2</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ41">
+        <f>CORREL(AE40:AE42, AG40:AG42)</f>
+        <v>0.95382096647653203</v>
+      </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A42">
         <v>3</v>
       </c>
-      <c r="B36">
+      <c r="B42">
         <v>1.9098905999999999E-2</v>
       </c>
-      <c r="C36">
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D42">
         <v>39.341079999999998</v>
       </c>
-      <c r="K36" t="s">
+      <c r="E42">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="O42">
+        <v>12</v>
+      </c>
+      <c r="P42">
+        <v>5.5304152000000002E-2</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="R42">
+        <v>49.626179999999998</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AC42">
+        <v>3</v>
+      </c>
+      <c r="AD42">
+        <v>1.9098905999999999E-2</v>
+      </c>
+      <c r="AE42">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="AF42">
+        <v>39.341079999999998</v>
+      </c>
+      <c r="AG42">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A43">
         <v>4</v>
       </c>
-      <c r="L36">
-        <f>CORREL(C34:C45, B34:B45)</f>
-        <v>0.42538947809582711</v>
+      <c r="B43">
+        <v>3.0647164000000001E-2</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D43">
+        <v>12.56434</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AC43">
+        <v>5</v>
+      </c>
+      <c r="AD43">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="AE43">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AF43">
+        <v>24.90231</v>
+      </c>
+      <c r="AG43">
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>5</v>
+      </c>
+      <c r="B44">
+        <v>-1.361688E-2</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>24.90231</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="AC44">
+        <v>6</v>
+      </c>
+      <c r="AD44">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="AE44">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AF44">
+        <v>23.705850000000002</v>
+      </c>
+      <c r="AG44">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>6</v>
+      </c>
+      <c r="B45">
+        <v>8.6388139999999999E-3</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B38">
-        <v>-1.361688E-2</v>
-      </c>
-      <c r="C38">
-        <v>24.90231</v>
+      <c r="D45">
+        <v>23.705850000000002</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="AC45">
+        <v>8</v>
+      </c>
+      <c r="AD45">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="AE45">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="AF45">
+        <v>33.988129999999998</v>
+      </c>
+      <c r="AG45">
+        <f t="shared" si="5"/>
+        <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>6</v>
-      </c>
-      <c r="B39">
-        <v>8.6388139999999999E-3</v>
-      </c>
-      <c r="C39">
-        <v>23.705850000000002</v>
+    <row r="46" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>7</v>
+      </c>
+      <c r="B46">
+        <v>5.5768249999999998E-2</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="D46">
+        <v>44.66028</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="AC46">
+        <v>10</v>
+      </c>
+      <c r="AD46">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="AE46">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AF46">
+        <v>20.73094</v>
+      </c>
+      <c r="AG46">
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>8</v>
+      </c>
+      <c r="B47">
+        <v>1.9324102999999999E-2</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="D47">
+        <v>33.988129999999998</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="AC47">
+        <v>11</v>
+      </c>
+      <c r="AD47">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="AE47">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="AF47">
+        <v>10.663930000000001</v>
+      </c>
+      <c r="AG47">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>8</v>
-      </c>
-      <c r="B41">
-        <v>1.9324102999999999E-2</v>
-      </c>
-      <c r="C41">
-        <v>33.988129999999998</v>
+    <row r="48" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>10</v>
+      </c>
+      <c r="B48">
+        <v>-7.7793280000000003E-3</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>20.73094</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A42">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>11</v>
+      </c>
+      <c r="B49">
+        <v>3.3507642999999997E-2</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="D49">
+        <v>10.663930000000001</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>12</v>
+      </c>
+      <c r="B50">
+        <v>5.5304152000000002E-2</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B43">
-        <v>-7.7793280000000003E-3</v>
-      </c>
-      <c r="C43">
-        <v>20.73094</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A44">
+      <c r="D50">
+        <v>49.626179999999998</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="1"/>
         <v>11</v>
-      </c>
-      <c r="B44">
-        <v>3.3507642999999997E-2</v>
-      </c>
-      <c r="C44">
-        <v>10.663930000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
